--- a/exports/trend_1d/SOLARINDS_full_report.xlsx
+++ b/exports/trend_1d/SOLARINDS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>9.5</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42208</v>
+        <v>42209</v>
       </c>
       <c r="H2" t="n">
-        <v>769.91</v>
+        <v>761.29</v>
       </c>
       <c r="I2" t="n">
         <v>763.8037854398857</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K2" t="n">
-        <v>29.9</v>
+        <v>28.44</v>
       </c>
       <c r="L2" t="n">
         <v>1.77</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>11.73</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42367</v>
+        <v>42368</v>
       </c>
       <c r="H3" t="n">
-        <v>679.0700000000001</v>
+        <v>693.16</v>
       </c>
       <c r="I3" t="n">
         <v>683.9189724197968</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K3" t="n">
-        <v>10.8</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>6.13</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H4" t="n">
-        <v>680.41</v>
+        <v>672.5700000000001</v>
       </c>
       <c r="I4" t="n">
         <v>676.1782638153218</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.84</v>
+        <v>-2.97</v>
       </c>
       <c r="L4" t="n">
         <v>4.44</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.59</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42446</v>
+        <v>42447</v>
       </c>
       <c r="H5" t="n">
-        <v>664.47</v>
+        <v>681.01</v>
       </c>
       <c r="I5" t="n">
         <v>680.0586118393543</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2</v>
+        <v>-1.25</v>
       </c>
       <c r="L5" t="n">
         <v>4.09</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.77</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H6" t="n">
-        <v>644</v>
+        <v>639.15</v>
       </c>
       <c r="I6" t="n">
         <v>640.4936599737741</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.43</v>
+        <v>-6.15</v>
       </c>
       <c r="L6" t="n">
         <v>6.9</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42558</v>
+        <v>42559</v>
       </c>
       <c r="H7" t="n">
-        <v>647.59</v>
+        <v>649.75</v>
       </c>
       <c r="I7" t="n">
         <v>649.6785915982683</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.32</v>
+        <v>-1.66</v>
       </c>
       <c r="L7" t="n">
         <v>3.26</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>7.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42587</v>
+        <v>42590</v>
       </c>
       <c r="H8" t="n">
-        <v>633.7</v>
+        <v>625.65</v>
       </c>
       <c r="I8" t="n">
         <v>632.4058714734375</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.47</v>
+        <v>-3.71</v>
       </c>
       <c r="L8" t="n">
-        <v>2.89</v>
+        <v>4.54</v>
       </c>
       <c r="M8" t="n">
         <v>0.8100000000000001</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>8.49</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42611</v>
+        <v>42612</v>
       </c>
       <c r="H9" t="n">
-        <v>633.25</v>
+        <v>650.35</v>
       </c>
       <c r="I9" t="n">
         <v>649.4900050009036</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.21</v>
+        <v>-3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>2.88</v>
+        <v>4.69</v>
       </c>
       <c r="M9" t="n">
         <v>2.08</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42607</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>13.9</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43125</v>
+        <v>43129</v>
       </c>
       <c r="H10" t="n">
-        <v>1103.6</v>
+        <v>1095.75</v>
       </c>
       <c r="I10" t="n">
         <v>1102.253959293268</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="K10" t="n">
-        <v>69.69</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>7.59</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>349</v>
+        <v>350</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>18</v>
+      </c>
+      <c r="U10" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.13</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43186</v>
+        <v>43187</v>
       </c>
       <c r="H11" t="n">
-        <v>1052</v>
+        <v>1068.55</v>
       </c>
       <c r="I11" t="n">
         <v>1065.072932951615</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K11" t="n">
-        <v>3.99</v>
+        <v>2.48</v>
       </c>
       <c r="L11" t="n">
         <v>0.72</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.460000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43300</v>
+        <v>43301</v>
       </c>
       <c r="H12" t="n">
-        <v>1086.45</v>
+        <v>1079</v>
       </c>
       <c r="I12" t="n">
         <v>1084.16464790301</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K12" t="n">
-        <v>1.68</v>
+        <v>0.98</v>
       </c>
       <c r="L12" t="n">
         <v>5.67</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.6</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43308</v>
+        <v>43311</v>
       </c>
       <c r="H13" t="n">
-        <v>1155.85</v>
+        <v>1192.35</v>
       </c>
       <c r="I13" t="n">
         <v>1182.593224915983</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.12</v>
+        <v>-10.51</v>
       </c>
       <c r="L13" t="n">
-        <v>8.039999999999999</v>
+        <v>12.96</v>
       </c>
       <c r="M13" t="n">
         <v>1.5</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>11.17</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43350</v>
+        <v>43353</v>
       </c>
       <c r="H14" t="n">
-        <v>1156.35</v>
+        <v>1149.9</v>
       </c>
       <c r="I14" t="n">
         <v>1154.545930676087</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.02</v>
+        <v>-3.56</v>
       </c>
       <c r="L14" t="n">
-        <v>3.55</v>
+        <v>5.48</v>
       </c>
       <c r="M14" t="n">
         <v>1.79</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.58</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43447</v>
+        <v>43448</v>
       </c>
       <c r="H15" t="n">
-        <v>1038.7</v>
+        <v>1064.5</v>
       </c>
       <c r="I15" t="n">
         <v>1045.064431995157</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K15" t="n">
-        <v>9.67</v>
+        <v>7.43</v>
       </c>
       <c r="L15" t="n">
         <v>0.66</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43507</v>
+        <v>43508</v>
       </c>
       <c r="H16" t="n">
-        <v>977.25</v>
+        <v>965.15</v>
       </c>
       <c r="I16" t="n">
         <v>974.4045156153552</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.199999999999999</v>
+        <v>-9.33</v>
       </c>
       <c r="L16" t="n">
-        <v>8.69</v>
+        <v>10.19</v>
       </c>
       <c r="M16" t="n">
         <v>1.64</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>7.68</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H17" t="n">
-        <v>976.05</v>
+        <v>1042.85</v>
       </c>
       <c r="I17" t="n">
         <v>1002.359695545031</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.13</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>9.09</v>
       </c>
       <c r="M17" t="n">
         <v>2.51</v>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>6.84</v>
       </c>
       <c r="O17" t="n">
         <v>-1.24</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>11.55</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43678</v>
+        <v>43679</v>
       </c>
       <c r="H18" t="n">
-        <v>1091.8</v>
+        <v>1076.95</v>
       </c>
       <c r="I18" t="n">
         <v>1085.079412138028</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K18" t="n">
-        <v>4.69</v>
+        <v>3.27</v>
       </c>
       <c r="L18" t="n">
         <v>6</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.59</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43832</v>
+        <v>43833</v>
       </c>
       <c r="H19" t="n">
-        <v>1097.15</v>
+        <v>1118.35</v>
       </c>
       <c r="I19" t="n">
         <v>1101.083679054556</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.88</v>
+        <v>-3.84</v>
       </c>
       <c r="L19" t="n">
         <v>9.01</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>6</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>7.38</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43873</v>
+        <v>43874</v>
       </c>
       <c r="H20" t="n">
-        <v>1211.4</v>
+        <v>1185.85</v>
       </c>
       <c r="I20" t="n">
         <v>1185.9563783779</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>8.32</v>
+        <v>6.04</v>
       </c>
       <c r="L20" t="n">
         <v>3.17</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>14.71</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43991</v>
+        <v>43992</v>
       </c>
       <c r="H21" t="n">
-        <v>935.7</v>
+        <v>973.8</v>
       </c>
       <c r="I21" t="n">
         <v>955.884228724338</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K21" t="n">
-        <v>21.09</v>
+        <v>17.88</v>
       </c>
       <c r="L21" t="n">
         <v>7.86</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.44</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H22" t="n">
-        <v>1043.05</v>
+        <v>994.25</v>
       </c>
       <c r="I22" t="n">
         <v>1036.844766215273</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K22" t="n">
-        <v>7.11</v>
+        <v>2.1</v>
       </c>
       <c r="L22" t="n">
         <v>6.56</v>
@@ -1695,7 +1958,7 @@
         <v>3.91</v>
       </c>
       <c r="N22" t="n">
-        <v>3.19</v>
+        <v>4.68</v>
       </c>
       <c r="O22" t="n">
         <v>4.07</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.45</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44176</v>
+        <v>44179</v>
       </c>
       <c r="H23" t="n">
-        <v>1034.5</v>
+        <v>1088.55</v>
       </c>
       <c r="I23" t="n">
         <v>1081.879648480503</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.05</v>
+        <v>-9.48</v>
       </c>
       <c r="L23" t="n">
         <v>16.67</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44287</v>
+        <v>44291</v>
       </c>
       <c r="H24" t="n">
-        <v>1292.4</v>
+        <v>1247.7</v>
       </c>
       <c r="I24" t="n">
         <v>1268.346640582567</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K24" t="n">
-        <v>18.73</v>
+        <v>14.62</v>
       </c>
       <c r="L24" t="n">
         <v>5.19</v>
@@ -1809,7 +2096,7 @@
         <v>1.77</v>
       </c>
       <c r="N24" t="n">
-        <v>2.66</v>
+        <v>3.46</v>
       </c>
       <c r="O24" t="n">
         <v>5.22</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>14.22</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44343</v>
+        <v>44344</v>
       </c>
       <c r="H25" t="n">
-        <v>1337.45</v>
+        <v>1404.75</v>
       </c>
       <c r="I25" t="n">
         <v>1346.588823212879</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K25" t="n">
-        <v>-7.19</v>
+        <v>-12.59</v>
       </c>
       <c r="L25" t="n">
-        <v>11</v>
+        <v>15.86</v>
       </c>
       <c r="M25" t="n">
-        <v>2.69</v>
+        <v>6.17</v>
       </c>
       <c r="N25" t="n">
         <v>6.3</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.93</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H26" t="n">
-        <v>2502.95</v>
+        <v>2208.45</v>
       </c>
       <c r="I26" t="n">
         <v>2368.655270971959</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K26" t="n">
-        <v>78.18000000000001</v>
+        <v>57.21</v>
       </c>
       <c r="L26" t="n">
         <v>2.83</v>
@@ -1923,7 +2234,7 @@
         <v>2.59</v>
       </c>
       <c r="N26" t="n">
-        <v>4.79</v>
+        <v>11.77</v>
       </c>
       <c r="O26" t="n">
         <v>5.03</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>28.66</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44517</v>
+        <v>44518</v>
       </c>
       <c r="H27" t="n">
-        <v>2731.6</v>
+        <v>2777.1</v>
       </c>
       <c r="I27" t="n">
         <v>2773.087622982961</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K27" t="n">
-        <v>-23.69</v>
+        <v>-25.75</v>
       </c>
       <c r="L27" t="n">
-        <v>26.74</v>
+        <v>29.05</v>
       </c>
       <c r="M27" t="n">
         <v>3</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>14.11</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44547</v>
+        <v>44550</v>
       </c>
       <c r="H28" t="n">
-        <v>2550.75</v>
+        <v>2376</v>
       </c>
       <c r="I28" t="n">
         <v>2419.155905571196</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.15</v>
+        <v>-14.44</v>
       </c>
       <c r="L28" t="n">
-        <v>10.01</v>
+        <v>15.11</v>
       </c>
       <c r="M28" t="n">
         <v>4.19</v>
       </c>
       <c r="N28" t="n">
-        <v>4.84</v>
+        <v>6.85</v>
       </c>
       <c r="O28" t="n">
         <v>1.67</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>18.3</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44585</v>
+        <v>44586</v>
       </c>
       <c r="H29" t="n">
-        <v>2315.75</v>
+        <v>2480.25</v>
       </c>
       <c r="I29" t="n">
         <v>2437.588990067386</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n">
-        <v>2.54</v>
+        <v>-4.39</v>
       </c>
       <c r="L29" t="n">
-        <v>5.64</v>
+        <v>8.33</v>
       </c>
       <c r="M29" t="n">
         <v>1.64</v>
       </c>
       <c r="N29" t="n">
-        <v>4.57</v>
+        <v>7.1</v>
       </c>
       <c r="O29" t="n">
         <v>-6.85</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>13.88</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44701</v>
+        <v>44704</v>
       </c>
       <c r="H30" t="n">
-        <v>2797.35</v>
+        <v>2683.55</v>
       </c>
       <c r="I30" t="n">
         <v>2748.029206575358</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K30" t="n">
-        <v>12.79</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L30" t="n">
         <v>12.45</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>15.97</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44764</v>
+        <v>44767</v>
       </c>
       <c r="H31" t="n">
-        <v>2815.55</v>
+        <v>2837.8</v>
       </c>
       <c r="I31" t="n">
         <v>2835.042872198024</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K31" t="n">
-        <v>-4.92</v>
+        <v>-5.75</v>
       </c>
       <c r="L31" t="n">
         <v>9.24</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>6.86</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H32" t="n">
-        <v>3696.65</v>
+        <v>3441.85</v>
       </c>
       <c r="I32" t="n">
         <v>3517.108861157609</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K32" t="n">
-        <v>30.26</v>
+        <v>21.29</v>
       </c>
       <c r="L32" t="n">
         <v>5.74</v>
       </c>
       <c r="M32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="N32" t="n">
-        <v>3.08</v>
+        <v>6.89</v>
       </c>
       <c r="O32" t="n">
         <v>0.79</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>14.74</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44834</v>
+        <v>44837</v>
       </c>
       <c r="H33" t="n">
-        <v>3916.8</v>
+        <v>3972.55</v>
       </c>
       <c r="I33" t="n">
         <v>3949.347190216103</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K33" t="n">
-        <v>-13.8</v>
+        <v>-15.42</v>
       </c>
       <c r="L33" t="n">
-        <v>15.49</v>
+        <v>17.58</v>
       </c>
       <c r="M33" t="n">
         <v>1.86</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>13.55</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44889</v>
+        <v>44890</v>
       </c>
       <c r="H34" t="n">
-        <v>3886.2</v>
+        <v>3759.7</v>
       </c>
       <c r="I34" t="n">
         <v>3826.210214760732</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K34" t="n">
-        <v>-2.17</v>
+        <v>-5.36</v>
       </c>
       <c r="L34" t="n">
-        <v>4.09</v>
+        <v>5.58</v>
       </c>
       <c r="M34" t="n">
         <v>0.95</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>11.07</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44895</v>
+        <v>44896</v>
       </c>
       <c r="H35" t="n">
-        <v>3877.75</v>
+        <v>4078.55</v>
       </c>
       <c r="I35" t="n">
         <v>4049.867801423406</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>-3.14</v>
+        <v>-8.48</v>
       </c>
       <c r="L35" t="n">
-        <v>4.24</v>
+        <v>9</v>
       </c>
       <c r="M35" t="n">
-        <v>0.65</v>
+        <v>1.2</v>
       </c>
       <c r="N35" t="n">
-        <v>4.32</v>
+        <v>5.18</v>
       </c>
       <c r="O35" t="n">
         <v>-3.26</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>11.14</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44946</v>
+        <v>44949</v>
       </c>
       <c r="H36" t="n">
-        <v>4249.35</v>
+        <v>4084.7</v>
       </c>
       <c r="I36" t="n">
         <v>4098.640878190184</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K36" t="n">
-        <v>4.19</v>
+        <v>0.15</v>
       </c>
       <c r="L36" t="n">
         <v>4.67</v>
@@ -2493,7 +2924,7 @@
         <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.94</v>
+        <v>3.87</v>
       </c>
       <c r="O36" t="n">
         <v>5.18</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>10.74</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44973</v>
+        <v>44974</v>
       </c>
       <c r="H37" t="n">
-        <v>3941.7</v>
+        <v>4027.75</v>
       </c>
       <c r="I37" t="n">
         <v>3944.4755113772</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K37" t="n">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="L37" t="n">
         <v>4.84</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45012</v>
+        <v>45013</v>
       </c>
       <c r="H38" t="n">
-        <v>3752.6</v>
+        <v>3654.6</v>
       </c>
       <c r="I38" t="n">
         <v>3673.155335784468</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K38" t="n">
-        <v>-6.83</v>
+        <v>-9.26</v>
       </c>
       <c r="L38" t="n">
-        <v>7.87</v>
+        <v>9.85</v>
       </c>
       <c r="M38" t="n">
         <v>1.39</v>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>2.61</v>
       </c>
       <c r="O38" t="n">
         <v>2.18</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>9.859999999999999</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45132</v>
+        <v>45133</v>
       </c>
       <c r="H39" t="n">
-        <v>3779.65</v>
+        <v>3831.45</v>
       </c>
       <c r="I39" t="n">
         <v>3787.074365564179</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.42</v>
+        <v>-4.84</v>
       </c>
       <c r="L39" t="n">
         <v>8.140000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>5</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="H40" t="n">
-        <v>6536.35</v>
+        <v>6288.9</v>
       </c>
       <c r="I40" t="n">
         <v>6329.671955712292</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K40" t="n">
-        <v>70.59999999999999</v>
+        <v>64.14</v>
       </c>
       <c r="L40" t="n">
         <v>1.92</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>17.26</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45301</v>
+        <v>45302</v>
       </c>
       <c r="H41" t="n">
-        <v>6875.75</v>
+        <v>7347.05</v>
       </c>
       <c r="I41" t="n">
         <v>6938.466541037234</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K41" t="n">
-        <v>-9.33</v>
+        <v>-16.83</v>
       </c>
       <c r="L41" t="n">
-        <v>10.35</v>
+        <v>17.14</v>
       </c>
       <c r="M41" t="n">
         <v>3.61</v>
       </c>
       <c r="N41" t="n">
-        <v>5.66</v>
+        <v>6.85</v>
       </c>
       <c r="O41" t="n">
         <v>-3.79</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>13.45</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45315</v>
+        <v>45316</v>
       </c>
       <c r="H42" t="n">
-        <v>6624</v>
+        <v>6508.15</v>
       </c>
       <c r="I42" t="n">
         <v>6582.125467186378</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>-9.84</v>
+        <v>-11.42</v>
       </c>
       <c r="L42" t="n">
-        <v>10.1</v>
+        <v>12.15</v>
       </c>
       <c r="M42" t="n">
         <v>0.62</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>11.64</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45335</v>
+        <v>45336</v>
       </c>
       <c r="H43" t="n">
-        <v>6926</v>
+        <v>7020.1</v>
       </c>
       <c r="I43" t="n">
         <v>7002.862254425056</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.42</v>
+        <v>-7.87</v>
       </c>
       <c r="L43" t="n">
-        <v>8.15</v>
+        <v>9.83</v>
       </c>
       <c r="M43" t="n">
         <v>1.17</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.94</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H44" t="n">
-        <v>9860.299999999999</v>
+        <v>8705.6</v>
       </c>
       <c r="I44" t="n">
         <v>9080.716357473382</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K44" t="n">
-        <v>40.46</v>
+        <v>24.01</v>
       </c>
       <c r="L44" t="n">
         <v>6.68</v>
@@ -2949,7 +3476,7 @@
         <v>1.25</v>
       </c>
       <c r="N44" t="n">
-        <v>6.98</v>
+        <v>11.71</v>
       </c>
       <c r="O44" t="n">
         <v>1.36</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>23.95</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45474</v>
+        <v>45475</v>
       </c>
       <c r="H45" t="n">
-        <v>10098.6</v>
+        <v>11019.1</v>
       </c>
       <c r="I45" t="n">
         <v>10619.39448174632</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K45" t="n">
-        <v>-16</v>
+        <v>-26.57</v>
       </c>
       <c r="L45" t="n">
-        <v>17.45</v>
+        <v>28.54</v>
       </c>
       <c r="M45" t="n">
         <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>3.61</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="O45" t="n">
         <v>-11.71</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>14.11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45495</v>
+        <v>45496</v>
       </c>
       <c r="H46" t="n">
-        <v>10911.4</v>
+        <v>10721.95</v>
       </c>
       <c r="I46" t="n">
         <v>10767.93414059956</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.98</v>
+        <v>-2.7</v>
       </c>
       <c r="L46" t="n">
         <v>7.42</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>18.72</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45558</v>
+        <v>45559</v>
       </c>
       <c r="H47" t="n">
-        <v>11022.5</v>
+        <v>11407.65</v>
       </c>
       <c r="I47" t="n">
         <v>11345.81316987559</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.8</v>
+        <v>-6.4</v>
       </c>
       <c r="L47" t="n">
-        <v>6.78</v>
+        <v>7.77</v>
       </c>
       <c r="M47" t="n">
         <v>4.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>10.95</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45588</v>
+        <v>45589</v>
       </c>
       <c r="H48" t="n">
-        <v>10864.45</v>
+        <v>10425.5</v>
       </c>
       <c r="I48" t="n">
         <v>10486.7760541418</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.76</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L48" t="n">
         <v>9.279999999999999</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>16.01</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H49" t="n">
-        <v>10063.7</v>
+        <v>10194.65</v>
       </c>
       <c r="I49" t="n">
         <v>10153.43092781915</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K49" t="n">
-        <v>3.47</v>
+        <v>2.21</v>
       </c>
       <c r="L49" t="n">
         <v>11.24</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>11.69</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45698</v>
+        <v>45699</v>
       </c>
       <c r="H50" t="n">
-        <v>9174.950000000001</v>
+        <v>8816.25</v>
       </c>
       <c r="I50" t="n">
         <v>9002.565788893582</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>-10</v>
+        <v>-13.52</v>
       </c>
       <c r="L50" t="n">
-        <v>12.2</v>
+        <v>13.97</v>
       </c>
       <c r="M50" t="n">
         <v>0.61</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>16.25</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45723</v>
+        <v>45726</v>
       </c>
       <c r="H51" t="n">
-        <v>9486.5</v>
+        <v>9837.1</v>
       </c>
       <c r="I51" t="n">
         <v>9526.642662100467</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.6</v>
+        <v>-11.58</v>
       </c>
       <c r="L51" t="n">
-        <v>8.039999999999999</v>
+        <v>13.52</v>
       </c>
       <c r="M51" t="n">
         <v>1.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3.07</v>
+        <v>3.7</v>
       </c>
       <c r="O51" t="n">
         <v>-3.91</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.69</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="H52" t="n">
-        <v>16502</v>
+        <v>15904</v>
       </c>
       <c r="I52" t="n">
         <v>16361.99260613507</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K52" t="n">
-        <v>67.75</v>
+        <v>61.67</v>
       </c>
       <c r="L52" t="n">
         <v>3.99</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>10.23</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45874</v>
+        <v>45875</v>
       </c>
       <c r="H53" t="n">
-        <v>14920</v>
+        <v>15014</v>
       </c>
       <c r="I53" t="n">
         <v>14924.53613887425</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K53" t="n">
-        <v>6.19</v>
+        <v>5.6</v>
       </c>
       <c r="L53" t="n">
         <v>4.19</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>7.4</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45895</v>
+        <v>45897</v>
       </c>
       <c r="H54" t="n">
-        <v>14233</v>
+        <v>13813</v>
       </c>
       <c r="I54" t="n">
         <v>13902.34965476068</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>-5.2</v>
+        <v>-8</v>
       </c>
       <c r="L54" t="n">
-        <v>6.05</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M54" t="n">
         <v>0.43</v>
       </c>
       <c r="N54" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="O54" t="n">
         <v>0.63</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.85</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="H55" t="n">
-        <v>11911</v>
+        <v>12620</v>
       </c>
       <c r="I55" t="n">
         <v>12592.51102257012</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K55" t="n">
-        <v>13.77</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L55" t="n">
         <v>7.93</v>
@@ -3576,7 +4235,7 @@
         <v>1.69</v>
       </c>
       <c r="N55" t="n">
-        <v>3.58</v>
+        <v>5.95</v>
       </c>
       <c r="O55" t="n">
         <v>-2.95</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.74</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H56" t="n">
-        <v>13699</v>
+        <v>13159</v>
       </c>
       <c r="I56" t="n">
         <v>13589.09979647795</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K56" t="n">
-        <v>8.550000000000001</v>
+        <v>4.27</v>
       </c>
       <c r="L56" t="n">
         <v>6.31</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>13.3</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="H57" t="n">
-        <v>13662</v>
+        <v>13928</v>
       </c>
       <c r="I57" t="n">
         <v>13917.23788659842</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.82</v>
+        <v>-5.84</v>
       </c>
       <c r="L57" t="n">
-        <v>6.39</v>
+        <v>7.34</v>
       </c>
       <c r="M57" t="n">
         <v>4.43</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>13.02</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="H58" t="n">
-        <v>17277</v>
+        <v>16899</v>
       </c>
       <c r="I58" t="n">
         <v>17100.26307849024</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K58" t="n">
-        <v>24.05</v>
+        <v>21.33</v>
       </c>
       <c r="L58" t="n">
         <v>3.07</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>10.9</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H59" t="n">
-        <v>18467</v>
+        <v>19028</v>
       </c>
       <c r="I59" t="n">
         <v>18740.37325796521</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>-9.279999999999999</v>
+        <v>-12.6</v>
       </c>
       <c r="L59" t="n">
-        <v>12.27</v>
+        <v>13.17</v>
       </c>
       <c r="M59" t="n">
         <v>0.73</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>10.29</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="H60" t="n">
-        <v>22290</v>
+        <v>19250</v>
       </c>
       <c r="I60" t="n">
         <v>20766.4179589495</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K60" t="n">
-        <v>17.14</v>
+        <v>1.17</v>
       </c>
       <c r="L60" t="n">
         <v>6.37</v>
@@ -3861,7 +4580,7 @@
         <v>2.69</v>
       </c>
       <c r="N60" t="n">
-        <v>2.76</v>
+        <v>13.64</v>
       </c>
       <c r="O60" t="n">
         <v>3.04</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>30</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8879,7 +9618,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.5</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="6">
@@ -8889,7 +9628,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -8899,7 +9638,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="8">
@@ -8909,7 +9648,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -8919,7 +9658,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -8929,7 +9668,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -8939,7 +9678,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -8949,7 +9688,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -8959,7 +9698,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>33.9</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="14">
@@ -8969,7 +9708,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6.33</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="15">
@@ -8979,7 +9718,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.17</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -8989,7 +9728,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.79</v>
+        <v>-5.14</v>
       </c>
     </row>
     <row r="17">
@@ -8999,7 +9738,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.18000000000001</v>
+        <v>68.48999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -9009,7 +9748,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.8</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="19">
@@ -9019,7 +9758,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.18</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="20">
@@ -9029,7 +9768,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.39</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="21">
@@ -9039,7 +9778,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.74</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="22">
@@ -9049,7 +9788,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -9059,7 +9798,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -9069,7 +9808,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="25">
@@ -9089,7 +9828,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.35</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="27">
@@ -9099,7 +9838,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.57</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="28">
@@ -9109,7 +9848,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
